--- a/02-Referencias/Supply_bracofer/Maio/Relatorio Contas a Pagar 05-2026 - Normalizado.xlsx
+++ b/02-Referencias/Supply_bracofer/Maio/Relatorio Contas a Pagar 05-2026 - Normalizado.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S267"/>
+  <dimension ref="A1:S271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,7 +530,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000000 | [GIULIANA] EMBRATEL CLOUD OFFICE 365 05/2026 - S/NF - R$ 58,69 - VENCIMENTO EM 25/05/2026-PAGAMENTO VIA BOLETO BANCARIO--O NUMERO INFORMADO, É O NUMERO DA FATURA NO DOCUMENTO</t>
+          <t>REFERENTE A NF 000000000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000003 | PEDIDO(S) ASSOCIADO(S): [0030005338] Cristina - referente ao serviço do gesseiro que abriu o espaço para o marceneiro colocar estrutura do móvel e depois fechou .. vencimento 15/05 pagamento pix: 46007927000154 (ARCE GESSO) IMPOSTOS RETIDOS: ISSQN ($8,04) Valor total da nota $400 VALOR LÍQUIDO DA NOTA: $391,96</t>
+          <t>REFERENTE A NF 000000003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000005 | PEDIDO(S) ASSOCIADO(S): [0030005366] Referente a compra de CASTANHA P/ PORTAO DE ELEVACAO, no valor de R$1.500,00. Forma de pagamento pix, chave: 66235712000106</t>
+          <t>REFERENTE A NF 000000005</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000039 | PEDIDO(S) ASSOCIADO(S): [0030005333] Cristina - Referente a mão de obra da equipe de churrasco ( campanha mês do Serralheiro) realizado na data 30/04 NF 39 PIX 15/05</t>
+          <t>REFERENTE A NF 000000039</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000042 | PEDIDO(S) ASSOCIADO(S): [0030005342] Cristina - Referente a serviços de auditoria de estoque vencimento 15/05 Pagamento por pix: 55.599.387/0001-36</t>
+          <t>REFERENTE A NF 000000042</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000107 | PEDIDO(S) ASSOCIADO(S): [0030005322] CRISTINA - REF. GESTAO DE TRAFEGO GOOGLE - COMP 04/2026 NFS 107 VENC 15.05.2026 TRANSFERENCIA PIX CHAVE CNPJ: 52.596.265/0001-06 BANCO: 461 ASAAS I.P S.A AG: 0001 C/C: 4727065-7</t>
+          <t>REFERENTE A NF 000000107</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000119 | PEDIDO(S) ASSOCIADO(S): [0030005352] Referente a prestação de serviços de administração de redes sociais e conteúdos de Abril a Setembro. nf 119 boleto 15/05</t>
+          <t>REFERENTE A NF 000000119</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000196 | PEDIDO(S) ASSOCIADO(S): [0030005321] Cristina- Referente ao serviço de apoio à pesquisa intitulado “Projeto Modelagem baseada em dados de venda via Chatbots, no valor de R$ 11.880,00 Chave Pix: fundacte@gmail.com Favorecido: Fundacte- Fundação de Ciência Tecnologia e Ensino Instituição Bancária: Pag Bank Código do banco : 290- PagSeguro Internet S/A • Agência:0001 • Conta corrente:43023904-6 • CNPJ: 00.395.519/0001-16 O referido projeto possui vigência no período de fevereiro a agosto de 2026, conforme acordado com o professor Cássio NF 196 (3/6) 15/05</t>
+          <t>REFERENTE A NF 000000196</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000257 | PEDIDO(S) ASSOCIADO(S): [0030005367] Cristina- Referente a prestação de serviços do eletricista que fez a instalação elétrica da máquina de produzir tira raiada. Nf 257 - Pix cnpj: 43104416000162 25/05</t>
+          <t>REFERENTE A NF 000000257</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000310 | PEDIDO(S) ASSOCIADO(S): [0030005401]. (GIULIANA) NFS 310, VENCIMENTO 15/06/2026, PAGAMENTO VIA BOLETO BANCÁRIO. HONORÁRIO CONTÁBIL REF. AO MÊS 05/2026.</t>
+          <t>REFERENTE A NF 000000310</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/26</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000388 | PEDIDO(S) ASSOCIADO(S): [0030005341] Cristina - Referente a prestação de serviço de comunicação da Band Fm PERIODO DE VEICULACAO: 20/04/2026 A 15/05/2026 VEICULACAO DE 100 COMERCIAIS DE 30". NF 388 Boleto 18/05</t>
+          <t>REFERENTE A NF 000000388</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000428 | PEDIDO(S) ASSOCIADO(S): [0030005324] CRISTINA - REF. A COMPRA DE PÃO - NF 428 TRANSFERENCIA PIX 05240771000170 José Carlos Ignácio Presidente Prudente ME 15/05</t>
+          <t>REFERENTE A NF 000000428</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000500 | PEDIDO(S) ASSOCIADO(S): [0030005389]</t>
+          <t>REFERENTE A NF 000000500</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000989 | PEDIDO(S) ASSOCIADO(S): [0030005339] Cristina - Referente a compra de materiais de limpeza para reabastecimento de estoque. NF 989 BOLETO 05/06</t>
+          <t>REFERENTE A NF 000000989</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000001464 | PEDIDO(S) ASSOCIADO(S): [0030005328] Cristina - Referente a itens de chope para utilizar no churrasco realizado 30/04 prestigiando ao dia do serralheiro para colaboradores e clientes. nf 1464 boleto 14/05</t>
+          <t>REFERENTE A NF 000001464</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000164 | PEDIDO(S) ASSOCIADO(S): [0030005315]</t>
+          <t>REFERENTE A NF 000000164</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000164 | PEDIDO(S) ASSOCIADO(S): [0030005315]</t>
+          <t>REFERENTE A NF 000000164</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000001739 | PEDIDO(S) ASSOCIADO(S): [0030005332] Cristina - Referente a manutenção da polia eura 13 do pátio Braçofer. NF 1739 PIX 15/05 10.337.097/0001-86</t>
+          <t>REFERENTE A NF 000001739</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000003663 | PEDIDO(S) ASSOCIADO(S): [0030005345] Cristina - Referente a compra de alimentos para o churrasco em comemoração ao dia do serralheiro. Realizado em 30/04. Nf 3663 Boleto 15/05</t>
+          <t>REFERENTE A NF 000003663</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062227 | PEDIDO(S) ASSOCIADO(S): [0030005336]</t>
+          <t>REFERENTE A NF 000062227</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062227 | PEDIDO(S) ASSOCIADO(S): [0030005336]</t>
+          <t>REFERENTE A NF 000062227</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16/06/26</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062227 | PEDIDO(S) ASSOCIADO(S): [0030005336]</t>
+          <t>REFERENTE A NF 000062227</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062228 | PEDIDO(S) ASSOCIADO(S): [0030005335]</t>
+          <t>REFERENTE A NF 000062228</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062228 | PEDIDO(S) ASSOCIADO(S): [0030005335]</t>
+          <t>REFERENTE A NF 000062228</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16/06/26</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062228 | PEDIDO(S) ASSOCIADO(S): [0030005335]</t>
+          <t>REFERENTE A NF 000062228</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062529 | PEDIDO(S) ASSOCIADO(S): [0030005355]</t>
+          <t>REFERENTE A NF 000062529</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062529 | PEDIDO(S) ASSOCIADO(S): [0030005355]</t>
+          <t>REFERENTE A NF 000062529</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062529 | PEDIDO(S) ASSOCIADO(S): [0030005355]</t>
+          <t>REFERENTE A NF 000062529</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062583 | PEDIDO(S) ASSOCIADO(S): [0030005356]</t>
+          <t>REFERENTE A NF 000062583</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062583 | PEDIDO(S) ASSOCIADO(S): [0030005356]</t>
+          <t>REFERENTE A NF 000062583</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062583 | PEDIDO(S) ASSOCIADO(S): [0030005356]</t>
+          <t>REFERENTE A NF 000062583</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000063224 | PEDIDO(S) ASSOCIADO(S): [0030005407]</t>
+          <t>REFERENTE A NF 000063224</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000063224 | PEDIDO(S) ASSOCIADO(S): [0030005407]</t>
+          <t>REFERENTE A NF 000063224</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000063224 | PEDIDO(S) ASSOCIADO(S): [0030005407]</t>
+          <t>REFERENTE A NF 000063224</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009460 | PEDIDO(S) ASSOCIADO(S): [0030005350]</t>
+          <t>REFERENTE A NF 000009460</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009460 | PEDIDO(S) ASSOCIADO(S): [0030005350]</t>
+          <t>REFERENTE A NF 000009460</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009460 | PEDIDO(S) ASSOCIADO(S): [0030005350]</t>
+          <t>REFERENTE A NF 000009460</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009461 | PEDIDO(S) ASSOCIADO(S): [0030005390]</t>
+          <t>REFERENTE A NF 000009461</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/06/26</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009461 | PEDIDO(S) ASSOCIADO(S): [0030005390]</t>
+          <t>REFERENTE A NF 000009461</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009461 | PEDIDO(S) ASSOCIADO(S): [0030005390]</t>
+          <t>REFERENTE A NF 000009461</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009462 | PEDIDO(S) ASSOCIADO(S): [0030005391]</t>
+          <t>REFERENTE A NF 000009462</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/06/26</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009462 | PEDIDO(S) ASSOCIADO(S): [0030005391]</t>
+          <t>REFERENTE A NF 000009462</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009462 | PEDIDO(S) ASSOCIADO(S): [0030005391]</t>
+          <t>REFERENTE A NF 000009462</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000012979 | PEDIDO(S) ASSOCIADO(S): [0030005346] Cristina - Referente a serviço de telefonia NF 12979 Boleto 25/05</t>
+          <t>REFERENTE A NF 000012979</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000016193 | PEDIDO(S) ASSOCIADO(S): [0030005323] Cristina - Referente a Hospedagem de Cristiano para a contagem de materiais do estoque no pátio HOSPEDE: CRISTIANO DA SILVA CHECK-IN: 30/04/2026 CHECK-OUT: 03/05/2026 nf 16193 boleto 26/05</t>
+          <t>REFERENTE A NF 000016193</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000028472 | CRISTINA - REF EXAMES MEDICOS ADMISSIONAIS FUNCIONARIOS ALAN, CARLOS E LUCAS COMP ABRIL 2026. NF 28472 PAGTO VIA BOLETO BANCARIO PARA 15/05/2026.</t>
+          <t>REFERENTE A NF 000028472</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029804 | CRISTINA - REF CONSULTORIA MENSAL DE SEGURANÇA DO TRABALHO COMP MAIO 2026. NF 29804 PAGTO VIA BOLETO BANCARIO PARA 15/05/2026. (VALOR LIQUIDO 281,28)</t>
+          <t>REFERENTE A NF 000029804</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000456961 | PEDIDO(S) ASSOCIADO(S): [0030005348]</t>
+          <t>REFERENTE A NF 000456961</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000456961 | PEDIDO(S) ASSOCIADO(S): [0030005348]</t>
+          <t>REFERENTE A NF 000456961</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000456961 | PEDIDO(S) ASSOCIADO(S): [0030005348]</t>
+          <t>REFERENTE A NF 000456961</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000457689 | PEDIDO(S) ASSOCIADO(S): [0030005383]</t>
+          <t>REFERENTE A NF 000457689</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000457689 | PEDIDO(S) ASSOCIADO(S): [0030005383]</t>
+          <t>REFERENTE A NF 000457689</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000457689 | PEDIDO(S) ASSOCIADO(S): [0030005383]</t>
+          <t>REFERENTE A NF 000457689</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000046008 | PEDIDO(S) ASSOCIADO(S): [0030005316] CRISTINA - REF A MENSALIDADE DO SISTEMA NF 46008 BOLETO - NOTA COM RETENÇÃO DE IMPOSTO IRRF R$ 29,39 CSLL R$ 19,59 COFINS R$ 58,77 PIS R$ 12,73 VALOR A PAGAR R$ 1.838,52</t>
+          <t>REFERENTE A NF 000046008</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000046151 | PEDIDO(S) ASSOCIADO(S): [0030005368] CRISTINA - REF A SUPORTE EXTRA DO SISTEMA A CARGA DE INVENTÁRIO REALIZADO PELO VAGNER (CONSULTOR). NF 46151 BOLETO - NOTA COM RETENÇÃO DE IMPOSTO CONTRIBUIÇÕES SOCIAIS: $4,05 COFINS R$12,15 PIS R$ 2,63 VALOR A PAGAR R$ 386,17</t>
+          <t>REFERENTE A NF 000046151</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000084433 | PEDIDO(S) ASSOCIADO(S): [0030005374] Cristina - referente a compra de material para uso interno, Brocas para furar postinho NF: 84433 Boleto 15/06</t>
+          <t>REFERENTE A NF 000084433</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/26</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001182205 | PEDIDO(S) ASSOCIADO(S): [0030005283]</t>
+          <t>REFERENTE A NF 001182205</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001182205 | PEDIDO(S) ASSOCIADO(S): [0030005283]</t>
+          <t>REFERENTE A NF 001182205</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001182205 | PEDIDO(S) ASSOCIADO(S): [0030005283]</t>
+          <t>REFERENTE A NF 001182205</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001187077 | PEDIDO(S) ASSOCIADO(S): [0030005313]</t>
+          <t>REFERENTE A NF 001187077</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001187077 | PEDIDO(S) ASSOCIADO(S): [0030005313]</t>
+          <t>REFERENTE A NF 001187077</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001187077 | PEDIDO(S) ASSOCIADO(S): [0030005313]</t>
+          <t>REFERENTE A NF 001187077</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001660825 | PEDIDO(S) ASSOCIADO(S): [0030005393]</t>
+          <t>REFERENTE A NF 001660825</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001660825 | PEDIDO(S) ASSOCIADO(S): [0030005393]</t>
+          <t>REFERENTE A NF 001660825</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001660825 | PEDIDO(S) ASSOCIADO(S): [0030005393]</t>
+          <t>REFERENTE A NF 001660825</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/06/26</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000401 | PEDIDO(S) ASSOCIADO(S): [0030005353] Cristina - referente ao envio de amostras de um material que pretendemos trabalhar, quem está representando é o Cristiano ( inventário). Autorizado pelo Renato. NF 01 BOLETO 05/06</t>
+          <t>REFERENTE A NF 000000401</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000403878 | PEDIDO(S) ASSOCIADO(S): [0030005387]</t>
+          <t>REFERENTE A NF 000403878</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000451912 | [GIULIANA] REF A MENSALIDADE ACIPP-COMPETENCIA 04/2026 -VENCIMENTO 15/05/2026-PAGAMENTO VIA BOLETO BANCARIO</t>
+          <t>REFERENTE A NF 000451912</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000791405 | PEDIDO(S) ASSOCIADO(S): [0030005384]</t>
+          <t>REFERENTE A NF 000791405</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/06/26</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000791405 | PEDIDO(S) ASSOCIADO(S): [0030005384]</t>
+          <t>REFERENTE A NF 000791405</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000791405 | PEDIDO(S) ASSOCIADO(S): [0030005384]</t>
+          <t>REFERENTE A NF 000791405</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165307 | PEDIDO(S) ASSOCIADO(S): [0030005362]</t>
+          <t>REFERENTE A NF 000165307</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/26</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165307 | PEDIDO(S) ASSOCIADO(S): [0030005362]</t>
+          <t>REFERENTE A NF 000165307</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165307 | PEDIDO(S) ASSOCIADO(S): [0030005362]</t>
+          <t>REFERENTE A NF 000165307</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000057700 | PEDIDO(S) ASSOCIADO(S): [0030005231]</t>
+          <t>REFERENTE A NF 000057700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/26</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000057700 | PEDIDO(S) ASSOCIADO(S): [0030005231]</t>
+          <t>REFERENTE A NF 000057700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000057700 | PEDIDO(S) ASSOCIADO(S): [0030005231]</t>
+          <t>REFERENTE A NF 000057700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098776 | PEDIDO(S) ASSOCIADO(S): [0030005221]</t>
+          <t>REFERENTE A NF 000098776</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098776 | PEDIDO(S) ASSOCIADO(S): [0030005221]</t>
+          <t>REFERENTE A NF 000098776</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098776 | PEDIDO(S) ASSOCIADO(S): [0030005221]</t>
+          <t>REFERENTE A NF 000098776</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098777 | PEDIDO(S) ASSOCIADO(S): [0030005363]</t>
+          <t>REFERENTE A NF 000098777</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098777 | PEDIDO(S) ASSOCIADO(S): [0030005363]</t>
+          <t>REFERENTE A NF 000098777</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098777 | PEDIDO(S) ASSOCIADO(S): [0030005363]</t>
+          <t>REFERENTE A NF 000098777</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 027590003 | PEDIDO(S) ASSOCIADO(S): [0030005377] CRISTINA - REF A RECARGA DO GOOGLE VENC. 24/05 boleto</t>
+          <t>REFERENTE A NF 027590003</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000071810 | PEDIDO(S) ASSOCIADO(S): [0030005334] CRISTINA - REF A COMPRA DE CAFE NF 71810 BOLETO 05/06</t>
+          <t>REFERENTE A NF 000071810</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000013466 | PEDIDO(S) ASSOCIADO(S): [0030005369]</t>
+          <t>REFERENTE A NF 000013466</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000013466 | PEDIDO(S) ASSOCIADO(S): [0030005369]</t>
+          <t>REFERENTE A NF 000013466</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000013466 | PEDIDO(S) ASSOCIADO(S): [0030005369]</t>
+          <t>REFERENTE A NF 000013466</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014113 | PEDIDO(S) ASSOCIADO(S): [0030005378]</t>
+          <t>REFERENTE A NF 000014113</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014113 | PEDIDO(S) ASSOCIADO(S): [0030005378]</t>
+          <t>REFERENTE A NF 000014113</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014113 | PEDIDO(S) ASSOCIADO(S): [0030005378]</t>
+          <t>REFERENTE A NF 000014113</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014125 | PEDIDO(S) ASSOCIADO(S): [0030005364]</t>
+          <t>REFERENTE A NF 000014125</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014125 | PEDIDO(S) ASSOCIADO(S): [0030005364]</t>
+          <t>REFERENTE A NF 000014125</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014125 | PEDIDO(S) ASSOCIADO(S): [0030005364]</t>
+          <t>REFERENTE A NF 000014125</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014126 | PEDIDO(S) ASSOCIADO(S): [0030005376]</t>
+          <t>REFERENTE A NF 000014126</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014126 | PEDIDO(S) ASSOCIADO(S): [0030005376]</t>
+          <t>REFERENTE A NF 000014126</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014126 | PEDIDO(S) ASSOCIADO(S): [0030005376]</t>
+          <t>REFERENTE A NF 000014126</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014139 | PEDIDO(S) ASSOCIADO(S): [0030005392]</t>
+          <t>REFERENTE A NF 000014139</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014139 | PEDIDO(S) ASSOCIADO(S): [0030005392]</t>
+          <t>REFERENTE A NF 000014139</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014139 | PEDIDO(S) ASSOCIADO(S): [0030005392]</t>
+          <t>REFERENTE A NF 000014139</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000016346 | PEDIDO(S) ASSOCIADO(S): [0030005375] Cristina - Referente a compra de cintas para uso no patio NF: 16346 Boleto 17/06</t>
+          <t>REFERENTE A NF 000016346</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165537 | PEDIDO(S) ASSOCIADO(S): [0030005347] Cristina - Referente a compra de materiais de escritório para reabastecimento de estoque. NF 165537 BOLETO 25/05</t>
+          <t>REFERENTE A NF 000165537</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029231 | PEDIDO(S) ASSOCIADO(S): [0030005344]</t>
+          <t>REFERENTE A NF 000029231</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029231 | PEDIDO(S) ASSOCIADO(S): [0030005344]</t>
+          <t>REFERENTE A NF 000029231</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029231 | PEDIDO(S) ASSOCIADO(S): [0030005344]</t>
+          <t>REFERENTE A NF 000029231</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000333 | PEDIDO(S) ASSOCIADO(S): [0030005340] CRISTINA - REFERENTE A COMPRA DE MATERIAS EPÍS PARA REABASTECIMENTO DO ESTOQUE DE USO DOS COLABORADORES. NF 333 BOLETO 02/06</t>
+          <t>REFERENTE A NF 000000333</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000448575 | PEDIDO(S) ASSOCIADO(S): [0030005359] Cristina - Referente a compra de tomada para instalação da roletadeira no pátio. NF 448575 - BOLETO 13/06</t>
+          <t>REFERENTE A NF 000448575</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/26</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000468 | PEDIDO(S) ASSOCIADO(S): [0030005360] Cristina - Compra referente a reposição de tintas para organização de materiais do estoque. NF 468 BOLETO 2X</t>
+          <t>REFERENTE A NF 000000468</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000468 | PEDIDO(S) ASSOCIADO(S): [0030005360] Cristina - Compra referente a reposição de tintas para organização de materiais do estoque. NF 468 BOLETO 2X</t>
+          <t>REFERENTE A NF 000000468</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/26</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000005627 | PEDIDO(S) ASSOCIADO(S): [0030005357] Cristina - Referente a compra de uniformes para uso de colaboradores. NF 5627 Boleto 2x</t>
+          <t>REFERENTE A NF 000005627</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/06/26</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000005627 | PEDIDO(S) ASSOCIADO(S): [0030005357] Cristina - Referente a compra de uniformes para uso de colaboradores. NF 5627 Boleto 2x</t>
+          <t>REFERENTE A NF 000005627</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000006598 | PEDIDO(S) ASSOCIADO(S): [0030005329] Cristina - Referente a compra de refeição para café da manhã do pessoal presente para a contagem no dia 01/05 (sexta) NF6598 BOLETO 11/05</t>
+          <t>REFERENTE A NF 000006598</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000006599 | PEDIDO(S) ASSOCIADO(S): [0030005330] Cristina - Referente a compra de refeição para café da manhã do pessoal presente para a contagem no dia 02/05 (sábado) NF6599 BOLETO 11/05</t>
+          <t>REFERENTE A NF 000006599</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000006628 | PEDIDO(S) ASSOCIADO(S): [0030005331] Cristina - Referente a compra de refeição para café da manhã do pessoal presente para a contagem no dia 03/05 (domingo) NF6628 BOLETO 12/05</t>
+          <t>REFERENTE A NF 000006628</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001013752 | PEDIDO(S) ASSOCIADO(S): [0030005358]</t>
+          <t>REFERENTE A NF 001013752</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001013752 | PEDIDO(S) ASSOCIADO(S): [0030005358]</t>
+          <t>REFERENTE A NF 001013752</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001013752 | PEDIDO(S) ASSOCIADO(S): [0030005358]</t>
+          <t>REFERENTE A NF 001013752</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000405509 | PEDIDO(S) ASSOCIADO(S): [0030005373]</t>
+          <t>REFERENTE A NF 000405509</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000405509 | PEDIDO(S) ASSOCIADO(S): [0030005373]</t>
+          <t>REFERENTE A NF 000405509</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000405509 | PEDIDO(S) ASSOCIADO(S): [0030005373]</t>
+          <t>REFERENTE A NF 000405509</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16/06/26</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001014842 | PEDIDO(S) ASSOCIADO(S): [0030005380]</t>
+          <t>REFERENTE A NF 001014842</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001014842 | PEDIDO(S) ASSOCIADO(S): [0030005380]</t>
+          <t>REFERENTE A NF 001014842</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/06/26</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001014842 | PEDIDO(S) ASSOCIADO(S): [0030005380]</t>
+          <t>REFERENTE A NF 001014842</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>REF AJUDA DE CUSTO COMP MAIO 2026 | PAGTO REF AJUDA DE CUSTO ESTAGIARIA COMP MAIO 2026. AMANDA SANTOS SALOMÃO / BANCO: NUBANK / AG: 0001 / C/C 92051644-5 / CHAVE PIX: CPF 394.052.338-07</t>
+          <t>REF AJUDA DE CUSTO COMP MAIO 2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>referente a fatura ikatec | CRISTINA - REF A CONTRATAÇÃO DO SISTEMA DIGISAC VENCIMENTO 18/05 NOTA SERA EMITIDA APOS O PAGAMENTO</t>
+          <t>referente a fatura ikatec</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA | ESTORNO DE CREDITO DE COMPRA DEVOLVIDA Conta: 40518-4, Ag: 0337, Banco: Caixa Econômica Federal, Chave pix: 18997649207, Nome: LUIS FERNANDO CANO RIBOLI R$ 960,00</t>
+          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA | ESTORNO DE CREDITO DE COMPRA DEVOLVIDA Conta: 592540867-1, Ag: 2000, Banco: Caixa Econômica Federal, Chave pix: 18996055413, Nome: APARECIDO ALVES DE MOURA R$ 392,00</t>
+          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>referente a fatura 104187 | CRISTINA - REF A COMPRA DE ENERGIA INJETADA COMP. MÊS REFERÊNCIA 04/2026 - BOLETO BANCARIO VENCIMENTO 20/05- UC 9/2710610-3 e UC 9/4778547-2</t>
+          <t>referente a fatura 104187</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>REFERENTE A RECIBO | Cristina - Referente a quantia de R$ 1.200,00 (Hum mil e Duzentos reais) mais 5 convites no valor de R$ 400,00 (Quatrocentos Reais ) Referente patrocinio no XVI COSTELÃO DA AEAAPP para profissionais da aréa técnológica – AEAAPP, Associação dos Engenheiros, Arquitetos e Agrônomos de Presidente Prudente Solicitado por Renato/Zanuto Dados para pagamentos: Dados bancário para credito: Banco: Sicoob Paulista 456 Agência: 4446 - Conta: 13.369-8 ou Chave PIX/CNPJ: 44.860.666/0001-95 21/05</t>
+          <t>REFERENTE A RECIBO</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PAGAMENTO EM DUPLICIDADE | PAGAMENTO REALIZADO EM DUPLICIDADE EM 25/05, O VALOR NÃO SERÁ DEVOLVIDO EM CONTA, SERÁ TROCADO EM MERCADORIA NO PRÓXIMO PEDIDO (AINDA SEM DATA PREVISTA), ZANUTO E LUCAS CIENTE</t>
+          <t>PAGAMENTO EM DUPLICIDADE</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>LOCACAO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA CZB9H07 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 792</t>
+          <t>LOCACAO DE VEICULO</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>LOCAÇÃO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA HAR1F82 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 793</t>
+          <t>LOCAÇÃO DE VEICULO</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -17571,7 +17571,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA EUS0048 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 794</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA CCS0052 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 795</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -17733,7 +17733,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA DPS0050 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 796</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA DPS0051 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 797</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA ACS0049 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 798</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>LOCACAO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA EJZ7495 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 799</t>
+          <t>LOCACAO DE VEICULO</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18057,7 +18057,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>LOCACAO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA EJZ7496 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 800</t>
+          <t>LOCACAO DE VEICULO</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -18128,41 +18128,41 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FOLHAESTAGIO042026</t>
+          <t>D260610-004</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>REF FOLHA ESTAGIO COMP ABRIL 2026</t>
+          <t>referente a o.c 5418</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>REF FOLHA ESTAGIO COMP ABRIL 2026 | PAGTO REF FOLHA SALARIAL ESTAGIÁRIOS EDUARDO PEDRETTI E HELENA SOARES COMP ABRIL 2026.</t>
+          <t>referente a o.c 5418</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>06916551000186 - RSE COMERCIO DE FERRO ACO E LOCACAO DE EQUIPAMENTOS LTD</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>29/05/26</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="H226" t="n">
-        <v>2000</v>
+        <v>33750</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -18177,7 +18177,7 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>2000</v>
+        <v>33750</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -18186,64 +18186,64 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>02050101</t>
+          <t>02040101</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Salario</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>2000</v>
+        <v>33750</v>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="S226" t="n">
-        <v>2000</v>
+        <v>33750</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>IOF0526</t>
+          <t>D260610-005</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250</t>
+          <t>REF A OC 5417</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250 | IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250</t>
+          <t>REF A OC 5417</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>000024 - BANCO SANTANDER</t>
+          <t>06916551000186 - RSE COMERCIO DE FERRO ACO E LOCACAO DE EQUIPAMENTOS LTD</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>29/05/26</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>10/06/26</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>12111.4</v>
+        <v>12861.42</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -18258,7 +18258,7 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>12111.4</v>
+        <v>12861.42</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -18267,16 +18267,16 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>02040201</t>
+          <t>02040101</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Juros pagos</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>12111.4</v>
+        <v>12861.42</v>
       </c>
       <c r="R227" t="inlineStr">
         <is>
@@ -18284,47 +18284,47 @@
         </is>
       </c>
       <c r="S227" t="n">
-        <v>1631.41</v>
+        <v>12861.42</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>JR110526</t>
+          <t>D260615-004</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JUROS SALDO UTILIZ ATE LIMITE</t>
+          <t>referente a fatura ikatec</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>JUROS SALDO UTILIZ ATE LIMITE | JUROS DE UTILIZAÇÃO DE SALDO ROTATIVO DA CONTA. PERIODO 11/04 A 10/05 (CONTA NEGATIVA EM 04/05)</t>
+          <t>referente a fatura ikatec</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>000024 - BANCO SANTANDER</t>
+          <t>18716151000106 - IKATEC ENGENHARIA DE SOFTWARE LTDA</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>06/05/26</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>16/06/26</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>16/06/26</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>635</v>
+        <v>828</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -18339,7 +18339,7 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>635</v>
+        <v>828</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -18348,16 +18348,16 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>02040202</t>
+          <t>02040120</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Tarifas Bancarias</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>635</v>
+        <v>828</v>
       </c>
       <c r="R228" t="inlineStr">
         <is>
@@ -18365,47 +18365,47 @@
         </is>
       </c>
       <c r="S228" t="n">
-        <v>635</v>
+        <v>828</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>JRCG0526</t>
+          <t>FOLHAESTAGIO042026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250</t>
+          <t>REF FOLHA ESTAGIO COMP ABRIL 2026</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250 | PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250</t>
+          <t>REF FOLHA ESTAGIO COMP ABRIL 2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>000024 - BANCO SANTANDER</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>62795.35</v>
+        <v>2000</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -18420,7 +18420,7 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>62795.35</v>
+        <v>2000</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -18429,64 +18429,64 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>02040201</t>
+          <t>02050101</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Juros pagos</t>
+          <t>Salario</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>62795.35</v>
+        <v>2000</v>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="S229" t="n">
-        <v>8458.530000000001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NF 000.000.006</t>
+          <t>IOF0526</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000006</t>
+          <t>IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000006 | [GIULIANA] REF AO SERVICOS PRESTADOS POR ANDERSON ZANUTO-SOLICITADO POR ADRIANA NOGUEIRA-COMPETENCIA 05/2026-NF 000.000.006 VALOR TOTAL R$ 12.000,00 - VENCIMENTO EM 05/06/2026-PAGAMENTO VIA TRANSFERENCIA/PIX-CHAVE PIX: 57703733000100</t>
+          <t>IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
+          <t>000024 - BANCO SANTANDER</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>12000</v>
+        <v>12111.4</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -18501,7 +18501,7 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>12000</v>
+        <v>12111.4</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -18510,16 +18510,16 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>02010101</t>
+          <t>02040201</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Serviços</t>
+          <t>Juros pagos</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>12000</v>
+        <v>12111.4</v>
       </c>
       <c r="R230" t="inlineStr">
         <is>
@@ -18527,47 +18527,47 @@
         </is>
       </c>
       <c r="S230" t="n">
-        <v>12000</v>
+        <v>1631.41</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>NF 000.000.016</t>
+          <t>ISS052026G3S05(AM)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000016</t>
+          <t>ISS TOMADOR RETIDO REFERENTE AO MÊS MAIO/2026 - NFS 3. PRESTAÇÃO DE SERVIÇO EM ALVARES MACHADO.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000016 | PEDIDO(S) ASSOCIADO(S): [0030005386]</t>
+          <t>ISS TOMADOR RETIDO REFERENTE AO MÊS MAIO/2026 - NFS 3. PRESTAÇÃO DE SERVIÇO EM ALVARES MACHADO.</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>40840620000153 - SILVA &amp; FARIAS TREINAMENTOS LTDA</t>
+          <t>43206424000110 - MUNICIPIO DE ALVARES MACHADO</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>26/05/26</t>
+          <t>31/05/26</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>17/06/26</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H231" t="n">
-        <v>5490</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -18582,7 +18582,7 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>5490</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -18591,16 +18591,16 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>02010101</t>
+          <t>02060301</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Serviços</t>
+          <t>ISS</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>5490</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R231" t="inlineStr">
         <is>
@@ -18608,47 +18608,47 @@
         </is>
       </c>
       <c r="S231" t="n">
-        <v>5490</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NF 000.000.098</t>
+          <t>JR110526</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000098</t>
+          <t>JUROS SALDO UTILIZ ATE LIMITE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000098 | PEDIDO(S) ASSOCIADO(S): [0030005388]</t>
+          <t>JUROS SALDO UTILIZ ATE LIMITE</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>42002078000195 - CS ADMINISTRACAO E SERVICOS LTDA</t>
+          <t>000024 - BANCO SANTANDER</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>26/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="H232" t="n">
-        <v>1073.33</v>
+        <v>635</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -18663,7 +18663,7 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>1073.33</v>
+        <v>635</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -18672,16 +18672,16 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>02010101</t>
+          <t>02040202</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Serviços</t>
+          <t>Tarifas Bancarias</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>1073.33</v>
+        <v>635</v>
       </c>
       <c r="R232" t="inlineStr">
         <is>
@@ -18689,47 +18689,47 @@
         </is>
       </c>
       <c r="S232" t="n">
-        <v>1073.33</v>
+        <v>635</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NF 000.000.205</t>
+          <t>JRCG0526</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000205</t>
+          <t>PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000205 | PEDIDO(S) ASSOCIADO(S): [0030005382]</t>
+          <t>PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>39933208000107 - H B BOSSOLANI SERVICOS ADMINISTRATIVOS</t>
+          <t>000024 - BANCO SANTANDER</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>22/05/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>03/06/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="H233" t="n">
-        <v>1149.06</v>
+        <v>62795.35</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -18744,7 +18744,7 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>1149.06</v>
+        <v>62795.35</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -18753,16 +18753,16 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>02010101</t>
+          <t>02040201</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Serviços</t>
+          <t>Juros pagos</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>1149.06</v>
+        <v>62795.35</v>
       </c>
       <c r="R233" t="inlineStr">
         <is>
@@ -18770,47 +18770,47 @@
         </is>
       </c>
       <c r="S233" t="n">
-        <v>1149.06</v>
+        <v>8458.530000000001</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PED-0067386001</t>
+          <t>NF 000.000.006</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000025823</t>
+          <t>REFERENTE A NF 000000006</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000025823 | PEDIDO(S) ASSOCIADO(S): [0030005354] Cristina - Compra de material utilizado para cano que foi danificado durante o conserto da área afetada pelo deslizamento do barranco. NF 25823 - BOLETO 13/05</t>
+          <t>REFERENTE A NF 000000006</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>57832180000195 - NELBRA MATERIAIS PARA CONSTRUCAO LTDA</t>
+          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>01/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>13/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>13/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="H234" t="n">
-        <v>93.39</v>
+        <v>12000</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -18825,7 +18825,7 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>93.39</v>
+        <v>12000</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -18834,64 +18834,64 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>02020103</t>
+          <t>02010101</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Desp. e Materiais Diveros</t>
+          <t>Serviços</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>93.39</v>
+        <v>12000</v>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="S234" t="n">
-        <v>93.39</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PENSÃOG3S050426</t>
+          <t>NF 000.000.016</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>REF PENSÃO FILHA FUNCIONARIO COMP ABRIL 2026</t>
+          <t>REFERENTE A NF 000000016</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>REF PENSÃO FILHA FUNCIONARIO COMP ABRIL 2026 | PAGTO REF CRÉDITO DE PENSÃO ALIMENTÍCIA FILHA FUNCIONARIO LUIS HENRIQUE SEMENSATO COMP ABRIL 2026. RENATA PERES NUNES: CPF: 371.144.288-98 // BANCO: ITAÚ // AGÊNCIA: 0203 // CONTA: 64310-1 // CHAVE PIX: re.pnunes6@gmail.com</t>
+          <t>REFERENTE A NF 000000016</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>37114428898 - RENATA PERES NUNES</t>
+          <t>40840620000153 - SILVA &amp; FARIAS TREINAMENTOS LTDA</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>26/05/26</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>500</v>
+        <v>5490</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -18906,7 +18906,7 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>500</v>
+        <v>5490</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -18915,64 +18915,64 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>02050109</t>
+          <t>02010101</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Pensão Alimenticia</t>
+          <t>Serviços</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>500</v>
+        <v>5490</v>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Operacional</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="S235" t="n">
-        <v>500</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PIXANIVERSARIO0526</t>
+          <t>NF 000.000.098</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA  AP LIMA QUEIRÓZ</t>
+          <t>REFERENTE A NF 000000098</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA  AP LIMA QUEIRÓZ | PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA APARECIDA LIMA QUEIROZ Agência 0337 Banco caixa Conta poupança 765383386-2 Chave Pix CPF 44533028861</t>
+          <t>REFERENTE A NF 000000098</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>42002078000195 - CS ADMINISTRACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>26/05/26</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>150</v>
+        <v>1073.33</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>150</v>
+        <v>1073.33</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -18996,16 +18996,16 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>02050101</t>
+          <t>02010101</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Salario</t>
+          <t>Serviços</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>150</v>
+        <v>1073.33</v>
       </c>
       <c r="R236" t="inlineStr">
         <is>
@@ -19013,47 +19013,47 @@
         </is>
       </c>
       <c r="S236" t="n">
-        <v>150</v>
+        <v>1073.33</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RESCISÃOESTAGIO052</t>
+          <t>NF 000.000.205</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 - HELENA</t>
+          <t>REFERENTE A NF 000000205</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 - HELENA | PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 HELENA SOARES GOES DA SILVA BANCO C6 BANK AG 0001 C/C 38210981-3 PIX 50500800880</t>
+          <t>REFERENTE A NF 000000205</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>39933208000107 - H B BOSSOLANI SERVICOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>22/05/26</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>29/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>29/05/26</t>
+          <t>03/06/26</t>
         </is>
       </c>
       <c r="H237" t="n">
-        <v>1683.33</v>
+        <v>1149.06</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>1683.33</v>
+        <v>1149.06</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -19077,16 +19077,16 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>02050108</t>
+          <t>02010101</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Rescisões</t>
+          <t>Serviços</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>1683.33</v>
+        <v>1149.06</v>
       </c>
       <c r="R237" t="inlineStr">
         <is>
@@ -19094,47 +19094,47 @@
         </is>
       </c>
       <c r="S237" t="n">
-        <v>1683.33</v>
+        <v>1149.06</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RESCSISÃOMAIO26</t>
+          <t>PED-0067386001</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26</t>
+          <t>REFERENTE A NF 000025823</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26 | PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26 - EDUARDO PEDRETTI ARRUDA RONCHESEL - ESTAGIO FINANCEIRO - BANCO INTER AG 0001 - C/C 18992669-4 - PIX 18997314402</t>
+          <t>REFERENTE A NF 000025823</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>57832180000195 - NELBRA MATERIAIS PARA CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>18/05/26</t>
+          <t>01/05/26</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>18/05/26</t>
+          <t>13/05/26</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>18/05/26</t>
+          <t>13/05/26</t>
         </is>
       </c>
       <c r="H238" t="n">
-        <v>650</v>
+        <v>93.39</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -19149,7 +19149,7 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>650</v>
+        <v>93.39</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -19158,45 +19158,45 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>02050108</t>
+          <t>02020103</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Rescisões</t>
+          <t>Desp. e Materiais Diveros</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>650</v>
+        <v>93.39</v>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="S238" t="n">
-        <v>650</v>
+        <v>93.39</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RKM05052026</t>
+          <t>PENSÃOG3S050426</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>REEMBOLSO ANDERSON ZANUTO</t>
+          <t>REF PENSÃO FILHA FUNCIONARIO COMP ABRIL 2026</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>REEMBOLSO ANDERSON ZANUTO | REFERENTE AO RELATORIO DE REEMBOLSO POR QUILOMETRAGEM DO ANDERSON ZANUTO NO PERÍODO DE 02/04/2026 A 29/04/2026 PAGAMENTO VIA TRANSFERENCIA/PIX CHAVE PIX: 57703733000100</t>
+          <t>REF PENSÃO FILHA FUNCIONARIO COMP ABRIL 2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
+          <t>37114428898 - RENATA PERES NUNES</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19206,16 +19206,16 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>1184.9</v>
+        <v>500</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -19230,7 +19230,7 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>1184.9</v>
+        <v>500</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -19239,64 +19239,64 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>02020205</t>
+          <t>02050109</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Despesas de Viagens</t>
+          <t>Pensão Alimenticia</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>1184.9</v>
+        <v>500</v>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Operacional</t>
         </is>
       </c>
       <c r="S239" t="n">
-        <v>1184.9</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SEGUROVIDAG3S0426</t>
+          <t>PIXANIVERSARIO0526</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>REF SEGURO DE VIDA COMP MAIO 2026</t>
+          <t>PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA  AP LIMA QUEIRÓZ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>REF SEGURO DE VIDA COMP MAIO 2026 | PAGTO REF SEGURO DE VIDA FUNCIONARIOS COMP MAIO 2026.</t>
+          <t>PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA  AP LIMA QUEIRÓZ</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>42283770000139 - ICATU SEGUROS S/A</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>22/05/26</t>
+          <t>28/05/26</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>28/05/26</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>28/05/26</t>
         </is>
       </c>
       <c r="H240" t="n">
-        <v>510.43</v>
+        <v>150</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -19311,7 +19311,7 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>510.43</v>
+        <v>150</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -19320,16 +19320,16 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>02060405</t>
+          <t>02050101</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Seguro Trabalho</t>
+          <t>Salario</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>510.43</v>
+        <v>150</v>
       </c>
       <c r="R240" t="inlineStr">
         <is>
@@ -19337,47 +19337,47 @@
         </is>
       </c>
       <c r="S240" t="n">
-        <v>56.15</v>
+        <v>150</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SEMPARARG3S050526</t>
+          <t>RESCISÃOESTAGIO052</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>REF SEM PARAR COMP MAIO 2026</t>
+          <t>PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 - HELENA</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>REF SEM PARAR COMP MAIO 2026 | PAGTO REF MENSALIDADE BENEFICIO SEM PARAR COMPETENCIA MAIO 2026.</t>
+          <t>PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 - HELENA</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>00288916001080 - VB-SERVICOS COMERCIO E ADMINISTRACAO LTDA</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>20/05/26</t>
+          <t>28/05/26</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>29/05/26</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>29/05/26</t>
         </is>
       </c>
       <c r="H241" t="n">
-        <v>10437.74</v>
+        <v>1683.33</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
@@ -19392,7 +19392,7 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>10437.74</v>
+        <v>1683.33</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -19401,64 +19401,64 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>02050202</t>
+          <t>02050108</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Aux Transporte</t>
+          <t>Rescisões</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>5218.87</v>
+        <v>1683.33</v>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="S241" t="n">
-        <v>1148.15</v>
+        <v>1683.33</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SINDICATOG3S04261</t>
+          <t>RESCSISÃOMAIO26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>REF SINDICATO COMP ABRIL 2026.</t>
+          <t>PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>REF SINDICATO COMP ABRIL 2026. | PAGTO REF SINDICATO CONTRIBUIÇÃO NEGOCIAL DESCONTO EM FOLHA COMP ABRIL 2026.</t>
+          <t>PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>11432305000199 - SINDICATO DOS TRAB. TRANSP. TERRESTRES DE PRES. PRUDENT</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>08/05/26</t>
+          <t>18/05/26</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>10/05/26</t>
+          <t>18/05/26</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>18/05/26</t>
         </is>
       </c>
       <c r="H242" t="n">
-        <v>108.96</v>
+        <v>650</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
@@ -19473,7 +19473,7 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>108.96</v>
+        <v>650</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -19482,64 +19482,64 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>02060403</t>
+          <t>02050108</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Sindical</t>
+          <t>Rescisões</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>108.96</v>
+        <v>650</v>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Logistica</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="S242" t="n">
-        <v>108.96</v>
+        <v>650</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>SINDICATOG3S050426</t>
+          <t>RKM05052026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>REF SINDICATO COMP ABRIL 2026.</t>
+          <t>REEMBOLSO ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>REF SINDICATO COMP ABRIL 2026. | PAGTO REF SINDICATO CONTRIBUIÇÃO ASSISTENCIAL DESCONTO EM FOLHA COMP ABRIL 2026.</t>
+          <t>REEMBOLSO ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>55354849000155 - SINDICATO EMPREGADOS COMERCIO DE PRESIDENTE PRUDEN</t>
+          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>08/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="H243" t="n">
-        <v>445.71</v>
+        <v>1184.9</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
@@ -19554,7 +19554,7 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>445.71</v>
+        <v>1184.9</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
@@ -19563,64 +19563,64 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>02060403</t>
+          <t>02020205</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Sindical</t>
+          <t>Despesas de Viagens</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445.71</v>
+        <v>1184.9</v>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="S243" t="n">
-        <v>57.94</v>
+        <v>1184.9</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TAR040526</t>
+          <t>SEGUROVIDAG3S0426</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES</t>
+          <t>REF SEGURO DE VIDA COMP MAIO 2026</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES</t>
+          <t>REF SEGURO DE VIDA COMP MAIO 2026</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>42283770000139 - ICATU SEGUROS S/A</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>22/05/26</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>04/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="H244" t="n">
-        <v>41.4</v>
+        <v>510.43</v>
       </c>
       <c r="I244" t="n">
         <v>0</v>
@@ -19635,7 +19635,7 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>41.4</v>
+        <v>510.43</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -19644,16 +19644,16 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>02040202</t>
+          <t>02060405</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Tarifas Bancarias</t>
+          <t>Seguro Trabalho</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>41.4</v>
+        <v>510.43</v>
       </c>
       <c r="R244" t="inlineStr">
         <is>
@@ -19661,47 +19661,47 @@
         </is>
       </c>
       <c r="S244" t="n">
-        <v>41.4</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TAR050526</t>
+          <t>SEMPARARG3S050526</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES</t>
+          <t>REF SEM PARAR COMP MAIO 2026</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES</t>
+          <t>REF SEM PARAR COMP MAIO 2026</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>00288916001080 - VB-SERVICOS COMERCIO E ADMINISTRACAO LTDA</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>20/05/26</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>05/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="H245" t="n">
-        <v>6.3</v>
+        <v>10437.74</v>
       </c>
       <c r="I245" t="n">
         <v>0</v>
@@ -19716,7 +19716,7 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>6.3</v>
+        <v>10437.74</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -19725,64 +19725,64 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>02040202</t>
+          <t>02050202</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Tarifas Bancarias</t>
+          <t>Aux Transporte</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>6.3</v>
+        <v>5218.87</v>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="S245" t="n">
-        <v>6.3</v>
+        <v>1148.15</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TAR060526</t>
+          <t>SINDICATOG3S04261</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES</t>
+          <t>REF SINDICATO COMP ABRIL 2026.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES</t>
+          <t>REF SINDICATO COMP ABRIL 2026.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>11432305000199 - SINDICATO DOS TRAB. TRANSP. TERRESTRES DE PRES. PRUDENT</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>06/05/26</t>
+          <t>08/05/26</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>06/05/26</t>
+          <t>10/05/26</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>06/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="H246" t="n">
-        <v>14.4</v>
+        <v>108.96</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
@@ -19797,7 +19797,7 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>14.4</v>
+        <v>108.96</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -19806,64 +19806,64 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>02040202</t>
+          <t>02060403</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Tarifas Bancarias</t>
+          <t>Sindical</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>14.4</v>
+        <v>108.96</v>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Logistica</t>
         </is>
       </c>
       <c r="S246" t="n">
-        <v>14.4</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TAR070526</t>
+          <t>SINDICATOG3S050426</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES</t>
+          <t>REF SINDICATO COMP ABRIL 2026.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES</t>
+          <t>REF SINDICATO COMP ABRIL 2026.</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>55354849000155 - SINDICATO EMPREGADOS COMERCIO DE PRESIDENTE PRUDEN</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>08/05/26</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>07/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="H247" t="n">
-        <v>4.5</v>
+        <v>445.71</v>
       </c>
       <c r="I247" t="n">
         <v>0</v>
@@ -19878,7 +19878,7 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4.5</v>
+        <v>445.71</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -19887,16 +19887,16 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>02040202</t>
+          <t>02060403</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Tarifas Bancarias</t>
+          <t>Sindical</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>4.5</v>
+        <v>445.71</v>
       </c>
       <c r="R247" t="inlineStr">
         <is>
@@ -19904,23 +19904,23 @@
         </is>
       </c>
       <c r="S247" t="n">
-        <v>4.5</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TAR080526</t>
+          <t>TAR040526</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -19930,21 +19930,21 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>08/05/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>08/05/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>08/05/26</t>
+          <t>04/05/26</t>
         </is>
       </c>
       <c r="H248" t="n">
-        <v>17.1</v>
+        <v>41.4</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
@@ -19959,7 +19959,7 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>17.1</v>
+        <v>41.4</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>17.1</v>
+        <v>41.4</v>
       </c>
       <c r="R248" t="inlineStr">
         <is>
@@ -19985,23 +19985,23 @@
         </is>
       </c>
       <c r="S248" t="n">
-        <v>17.1</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TAR110526</t>
+          <t>TAR050526</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -20011,21 +20011,21 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>11/05/26</t>
+          <t>05/05/26</t>
         </is>
       </c>
       <c r="H249" t="n">
-        <v>36</v>
+        <v>6.3</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>36</v>
+        <v>6.3</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>36</v>
+        <v>6.3</v>
       </c>
       <c r="R249" t="inlineStr">
         <is>
@@ -20066,23 +20066,23 @@
         </is>
       </c>
       <c r="S249" t="n">
-        <v>36</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TAR12052026</t>
+          <t>TAR060526</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>TARIFA BAIXA DE TITULOS</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>TARIFA BAIXA DE TITULOS | TARIFA BAIXA DE TITULOS</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -20092,21 +20092,21 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>06/05/26</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>06/05/26</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>06/05/26</t>
         </is>
       </c>
       <c r="H250" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="I250" t="n">
         <v>0</v>
@@ -20121,7 +20121,7 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="R250" t="inlineStr">
         <is>
@@ -20147,23 +20147,23 @@
         </is>
       </c>
       <c r="S250" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TAR120526</t>
+          <t>TAR070526</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -20173,21 +20173,21 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>07/05/26</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="I251" t="n">
         <v>0</v>
@@ -20202,7 +20202,7 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="N251" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="R251" t="inlineStr">
         <is>
@@ -20228,23 +20228,23 @@
         </is>
       </c>
       <c r="S251" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TAR130526</t>
+          <t>TAR080526</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -20254,21 +20254,21 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>13/05/26</t>
+          <t>08/05/26</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>13/05/26</t>
+          <t>08/05/26</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>13/05/26</t>
+          <t>08/05/26</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
@@ -20283,7 +20283,7 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>
@@ -20309,23 +20309,23 @@
         </is>
       </c>
       <c r="S252" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TAR14052026</t>
+          <t>TAR110526</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>TARIFA BAIXA DE TITULOS</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>TARIFA BAIXA DE TITULOS | TARIFA BAIXA DE TITULOS</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -20335,21 +20335,21 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>14/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>14/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>14/05/26</t>
+          <t>11/05/26</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>0.1</v>
+        <v>36</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -20364,7 +20364,7 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>0.1</v>
+        <v>36</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>0.1</v>
+        <v>36</v>
       </c>
       <c r="R253" t="inlineStr">
         <is>
@@ -20390,23 +20390,23 @@
         </is>
       </c>
       <c r="S253" t="n">
-        <v>0.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TAR140526</t>
+          <t>TAR12052026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA BAIXA DE TITULOS</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA BAIXA DE TITULOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -20416,21 +20416,21 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>14/05/26</t>
+          <t>12/05/26</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>14/05/26</t>
+          <t>12/05/26</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>14/05/26</t>
+          <t>12/05/26</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>9.9</v>
+        <v>0.1</v>
       </c>
       <c r="I254" t="n">
         <v>0</v>
@@ -20445,7 +20445,7 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>9.9</v>
+        <v>0.1</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>9.9</v>
+        <v>0.1</v>
       </c>
       <c r="R254" t="inlineStr">
         <is>
@@ -20471,23 +20471,23 @@
         </is>
       </c>
       <c r="S254" t="n">
-        <v>9.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TAR150526</t>
+          <t>TAR120526</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -20497,21 +20497,21 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>15/05/26</t>
+          <t>12/05/26</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>15/05/26</t>
+          <t>12/05/26</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>15/05/26</t>
+          <t>12/05/26</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="I255" t="n">
         <v>0</v>
@@ -20526,7 +20526,7 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="N255" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
@@ -20552,23 +20552,23 @@
         </is>
       </c>
       <c r="S255" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TAR180526</t>
+          <t>TAR130526</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -20578,21 +20578,21 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>18/05/26</t>
+          <t>13/05/26</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>18/05/26</t>
+          <t>13/05/26</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>18/05/26</t>
+          <t>13/05/26</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>27</v>
+        <v>11.7</v>
       </c>
       <c r="I256" t="n">
         <v>0</v>
@@ -20607,7 +20607,7 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>27</v>
+        <v>11.7</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>27</v>
+        <v>11.7</v>
       </c>
       <c r="R256" t="inlineStr">
         <is>
@@ -20633,23 +20633,23 @@
         </is>
       </c>
       <c r="S256" t="n">
-        <v>27</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TAR190526</t>
+          <t>TAR14052026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
+          <t>TARIFA BAIXA DE TITULOS</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
+          <t>TARIFA BAIXA DE TITULOS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -20659,21 +20659,21 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>19/05/26</t>
+          <t>14/05/26</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>19/05/26</t>
+          <t>14/05/26</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>19/05/26</t>
+          <t>14/05/26</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="I257" t="n">
         <v>0</v>
@@ -20688,7 +20688,7 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="R257" t="inlineStr">
         <is>
@@ -20714,23 +20714,23 @@
         </is>
       </c>
       <c r="S257" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TAR200526</t>
+          <t>TAR140526</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -20740,21 +20740,21 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>20/05/26</t>
+          <t>14/05/26</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>20/05/26</t>
+          <t>14/05/26</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>20/05/26</t>
+          <t>14/05/26</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>18</v>
+        <v>9.9</v>
       </c>
       <c r="I258" t="n">
         <v>0</v>
@@ -20769,7 +20769,7 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>18</v>
+        <v>9.9</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>18</v>
+        <v>9.9</v>
       </c>
       <c r="R258" t="inlineStr">
         <is>
@@ -20795,23 +20795,23 @@
         </is>
       </c>
       <c r="S258" t="n">
-        <v>18</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TAR210526</t>
+          <t>TAR150526</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -20821,21 +20821,21 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>21/05/26</t>
+          <t>15/05/26</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>21/05/26</t>
+          <t>15/05/26</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>21/05/26</t>
+          <t>15/05/26</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>8.1</v>
+        <v>15.3</v>
       </c>
       <c r="I259" t="n">
         <v>0</v>
@@ -20850,7 +20850,7 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>8.1</v>
+        <v>15.3</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>8.1</v>
+        <v>15.3</v>
       </c>
       <c r="R259" t="inlineStr">
         <is>
@@ -20876,23 +20876,23 @@
         </is>
       </c>
       <c r="S259" t="n">
-        <v>8.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TAR220526</t>
+          <t>TAR180526</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -20902,21 +20902,21 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>22/05/26</t>
+          <t>18/05/26</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>22/05/26</t>
+          <t>18/05/26</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>22/05/26</t>
+          <t>18/05/26</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>16.2</v>
+        <v>27</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -20931,7 +20931,7 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>16.2</v>
+        <v>27</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>16.2</v>
+        <v>27</v>
       </c>
       <c r="R260" t="inlineStr">
         <is>
@@ -20957,23 +20957,23 @@
         </is>
       </c>
       <c r="S260" t="n">
-        <v>16.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TAR250526</t>
+          <t>TAR190526</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -20983,21 +20983,21 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>19/05/26</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>19/05/26</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>25/05/26</t>
+          <t>19/05/26</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>31.5</v>
+        <v>8.1</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -21012,7 +21012,7 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>31.5</v>
+        <v>8.1</v>
       </c>
       <c r="N261" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>31.5</v>
+        <v>8.1</v>
       </c>
       <c r="R261" t="inlineStr">
         <is>
@@ -21038,23 +21038,23 @@
         </is>
       </c>
       <c r="S261" t="n">
-        <v>31.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TAR260526</t>
+          <t>TAR200526</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -21064,21 +21064,21 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>26/05/26</t>
+          <t>20/05/26</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>26/05/26</t>
+          <t>20/05/26</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>26/05/26</t>
+          <t>20/05/26</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>11.7</v>
+        <v>18</v>
       </c>
       <c r="I262" t="n">
         <v>0</v>
@@ -21093,7 +21093,7 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>11.7</v>
+        <v>18</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>11.7</v>
+        <v>18</v>
       </c>
       <c r="R262" t="inlineStr">
         <is>
@@ -21119,23 +21119,23 @@
         </is>
       </c>
       <c r="S262" t="n">
-        <v>11.7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TAR270526</t>
+          <t>TAR210526</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -21145,21 +21145,21 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>27/05/26</t>
+          <t>21/05/26</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>27/05/26</t>
+          <t>21/05/26</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>27/05/26</t>
+          <t>21/05/26</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="I263" t="n">
         <v>0</v>
@@ -21174,7 +21174,7 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="N263" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="R263" t="inlineStr">
         <is>
@@ -21200,23 +21200,23 @@
         </is>
       </c>
       <c r="S263" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TAR280526</t>
+          <t>TAR220526</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -21226,21 +21226,21 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>22/05/26</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>22/05/26</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>28/05/26</t>
+          <t>22/05/26</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
@@ -21255,7 +21255,7 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="R264" t="inlineStr">
         <is>
@@ -21281,23 +21281,23 @@
         </is>
       </c>
       <c r="S264" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TAR290526</t>
+          <t>TAR250526</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -21307,21 +21307,21 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>29/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>29/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>29/05/26</t>
+          <t>25/05/26</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>23.4</v>
+        <v>31.5</v>
       </c>
       <c r="I265" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>23.4</v>
+        <v>31.5</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>23.4</v>
+        <v>31.5</v>
       </c>
       <c r="R265" t="inlineStr">
         <is>
@@ -21362,23 +21362,23 @@
         </is>
       </c>
       <c r="S265" t="n">
-        <v>23.4</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TF120526</t>
+          <t>TAR260526</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>RENOVACAO CH. ESP.</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>RENOVACAO CH. ESP. | REFERENTE A TARIFA RENOVAÇÃO DE CHEQUE ESPECIAL G3S 05</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -21388,21 +21388,21 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>26/05/26</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>26/05/26</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>12/05/26</t>
+          <t>26/05/26</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>50</v>
+        <v>11.7</v>
       </c>
       <c r="I266" t="n">
         <v>0</v>
@@ -21417,7 +21417,7 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>50</v>
+        <v>11.7</v>
       </c>
       <c r="N266" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>50</v>
+        <v>11.7</v>
       </c>
       <c r="R266" t="inlineStr">
         <is>
@@ -21443,87 +21443,411 @@
         </is>
       </c>
       <c r="S266" t="n">
-        <v>50</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>TAR270526</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>27/05/26</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>27/05/26</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>27/05/26</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>02040202</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Tarifas Bancarias</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="S267" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>TAR280526</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>28/05/26</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>28/05/26</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>28/05/26</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>02040202</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Tarifas Bancarias</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="S268" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>TAR290526</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>29/05/26</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>29/05/26</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>29/05/26</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>02040202</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Tarifas Bancarias</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="S269" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>TF120526</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>RENOVACAO CH. ESP.</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>RENOVACAO CH. ESP.</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>12/05/26</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>12/05/26</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>12/05/26</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>50</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
+        <v>50</v>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>02040202</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Tarifas Bancarias</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>50</v>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="S270" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>TF150526</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>TARIFA PLANO EMPRESARIAL E1</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>TARIFA PLANO EMPRESARIAL E1 | TARIFA PLANO EMPRESARIAL E1</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>TARIFA PLANO EMPRESARIAL E1</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
         <is>
           <t>60746948000112 - BANCO BRADESCO SA</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>15/05/26</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>15/05/26</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G271" t="inlineStr">
         <is>
           <t>15/05/26</t>
         </is>
       </c>
-      <c r="H267" t="n">
+      <c r="H271" t="n">
         <v>117.85</v>
       </c>
-      <c r="I267" t="n">
-        <v>0</v>
-      </c>
-      <c r="J267" t="n">
-        <v>0</v>
-      </c>
-      <c r="K267" t="n">
-        <v>0</v>
-      </c>
-      <c r="L267" t="n">
-        <v>0</v>
-      </c>
-      <c r="M267" t="n">
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
         <v>117.85</v>
       </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>003</t>
-        </is>
-      </c>
-      <c r="O267" t="inlineStr">
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
         <is>
           <t>02040202</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr">
+      <c r="P271" t="inlineStr">
         <is>
           <t>Tarifas Bancarias</t>
         </is>
       </c>
-      <c r="Q267" t="n">
+      <c r="Q271" t="n">
         <v>117.85</v>
       </c>
-      <c r="R267" t="inlineStr">
+      <c r="R271" t="inlineStr">
         <is>
           <t>Administrativo</t>
         </is>
       </c>
-      <c r="S267" t="n">
+      <c r="S271" t="n">
         <v>117.85</v>
       </c>
     </row>
